--- a/pokedata.xlsx
+++ b/pokedata.xlsx
@@ -595,9 +595,6 @@
       <c r="AB5" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH5">
-        <v>400</v>
-      </c>
       <c r="AQ5" t="str">
         <v>https://m.media-amazon.com/images/I/71nEO07j44L._AC_SL1001_.jpg</v>
       </c>
@@ -687,9 +684,6 @@
       <c r="AB6" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH6">
-        <v>450</v>
-      </c>
       <c r="AQ6" t="str">
         <v>https://m.media-amazon.com/images/I/71nEO07j44L._AC_SL1001_.jpg</v>
       </c>
@@ -779,9 +773,6 @@
       <c r="AB7" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH7">
-        <v>450</v>
-      </c>
       <c r="AQ7" t="str">
         <v>https://m.media-amazon.com/images/I/71nEO07j44L._AC_SL1001_.jpg</v>
       </c>
@@ -871,9 +862,6 @@
       <c r="AB8" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH8">
-        <v>1200</v>
-      </c>
       <c r="AQ8" t="str">
         <v>https://m.media-amazon.com/images/I/71nEO07j44L._AC_SL1001_.jpg</v>
       </c>
@@ -963,9 +951,6 @@
       <c r="AB9" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH9">
-        <v>2000</v>
-      </c>
       <c r="AQ9" t="str">
         <v>https://m.media-amazon.com/images/I/71nEO07j44L._AC_SL1001_.jpg</v>
       </c>
@@ -1055,9 +1040,6 @@
       <c r="AB10" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH10">
-        <v>4000</v>
-      </c>
       <c r="AQ10" t="str">
         <v>https://m.media-amazon.com/images/I/71nEO07j44L._AC_SL1001_.jpg</v>
       </c>
@@ -1147,9 +1129,6 @@
       <c r="AB11" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH11">
-        <v>6500</v>
-      </c>
       <c r="AQ11" t="str">
         <v>https://m.media-amazon.com/images/I/71nEO07j44L._AC_SL1001_.jpg</v>
       </c>
@@ -1239,9 +1218,6 @@
       <c r="AB12" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH12">
-        <v>4500</v>
-      </c>
       <c r="AQ12" t="str">
         <v>https://m.media-amazon.com/images/I/71nEO07j44L._AC_SL1001_.jpg</v>
       </c>
@@ -1331,9 +1307,6 @@
       <c r="AB13" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH13">
-        <v>2200</v>
-      </c>
       <c r="AQ13" t="str">
         <v>https://m.media-amazon.com/images/I/71nEO07j44L._AC_SL1001_.jpg</v>
       </c>
@@ -1423,9 +1396,6 @@
       <c r="AB14" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH14">
-        <v>450</v>
-      </c>
       <c r="AQ14" t="str">
         <v>https://m.media-amazon.com/images/I/71nEO07j44L._AC_SL1001_.jpg</v>
       </c>
@@ -1515,9 +1485,6 @@
       <c r="AB15" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH15">
-        <v>1270</v>
-      </c>
       <c r="AQ15" t="str">
         <v>https://m.media-amazon.com/images/I/71nEO07j44L._AC_SL1001_.jpg</v>
       </c>
@@ -1607,9 +1574,6 @@
       <c r="AB16" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH16">
-        <v>1500</v>
-      </c>
       <c r="AQ16" t="str">
         <v>https://m.media-amazon.com/images/I/71nEO07j44L._AC_SL1001_.jpg</v>
       </c>
@@ -1699,9 +1663,6 @@
       <c r="AB17" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH17">
-        <v>2050</v>
-      </c>
       <c r="AQ17" t="str">
         <v>https://m.media-amazon.com/images/I/71nEO07j44L._AC_SL1001_.jpg</v>
       </c>
@@ -1791,9 +1752,6 @@
       <c r="AB18" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH18">
-        <v>2050</v>
-      </c>
       <c r="AQ18" t="str">
         <v>https://m.media-amazon.com/images/I/71nEO07j44L._AC_SL1001_.jpg</v>
       </c>
@@ -1883,9 +1841,6 @@
       <c r="AB19" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH19">
-        <v>560</v>
-      </c>
       <c r="AQ19" t="str">
         <v>https://m.media-amazon.com/images/I/81Mu0fQ+ZML._AC_SL1500_.jpg</v>
       </c>
@@ -1975,9 +1930,6 @@
       <c r="AB20" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH20">
-        <v>2000</v>
-      </c>
       <c r="AQ20" t="str">
         <v>https://m.media-amazon.com/images/I/710hnW0LXlL._AC_SL1500_.jpg</v>
       </c>
@@ -2043,9 +1995,6 @@
       <c r="T21">
         <v>500</v>
       </c>
-      <c r="AH21">
-        <v>500</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -2132,9 +2081,6 @@
       <c r="AB22" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH22">
-        <v>1700</v>
-      </c>
       <c r="AQ22" t="str">
         <v>https://m.media-amazon.com/images/I/71qAykbLspL._AC_SL1500_.jpg</v>
       </c>
@@ -2224,9 +2170,6 @@
       <c r="AB23" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH23">
-        <v>260</v>
-      </c>
       <c r="AQ23" t="str">
         <v>https://m.media-amazon.com/images/I/710FmIk40ML._AC_SL1500_.jpg</v>
       </c>
@@ -2316,9 +2259,6 @@
       <c r="AB24" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH24">
-        <v>400</v>
-      </c>
       <c r="AQ24" t="str">
         <v>https://m.media-amazon.com/images/I/61XpE5Tgb+L._AC_SL1001_.jpg</v>
       </c>
@@ -2408,9 +2348,6 @@
       <c r="AB25" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH25">
-        <v>400</v>
-      </c>
       <c r="AQ25" t="str">
         <v>https://m.media-amazon.com/images/I/61XpE5Tgb+L._AC_SL1001_.jpg</v>
       </c>
@@ -2500,9 +2437,6 @@
       <c r="AB26" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH26">
-        <v>230</v>
-      </c>
       <c r="AQ26" t="str">
         <v>https://m.media-amazon.com/images/I/81kZGtd5UXL._AC_SL1500_.jpg</v>
       </c>
@@ -2592,9 +2526,6 @@
       <c r="AB27" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH27">
-        <v>185</v>
-      </c>
       <c r="AQ27" t="str">
         <v>https://m.media-amazon.com/images/I/81kZGtd5UXL._AC_SL1500_.jpg</v>
       </c>
@@ -2684,9 +2615,6 @@
       <c r="AB28" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH28">
-        <v>450</v>
-      </c>
       <c r="AQ28" t="str">
         <v>https://m.media-amazon.com/images/I/81P+gqG8k2S._AC_SL1500_.jpg</v>
       </c>
@@ -2776,9 +2704,6 @@
       <c r="AB29" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH29">
-        <v>430</v>
-      </c>
       <c r="AQ29" t="str">
         <v>https://m.media-amazon.com/images/I/81P+gqG8k2S._AC_SL1500_.jpg</v>
       </c>
@@ -2868,9 +2793,6 @@
       <c r="AB30" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH30">
-        <v>470</v>
-      </c>
       <c r="AQ30" t="str">
         <v>https://m.media-amazon.com/images/I/61Yb2nb6B8L._AC_SL1500_.jpg</v>
       </c>
@@ -2960,9 +2882,6 @@
       <c r="AB31" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH31">
-        <v>300</v>
-      </c>
       <c r="AQ31" t="str">
         <v>https://m.media-amazon.com/images/I/81pW2PE9OKL._AC_SL1500_.jpg</v>
       </c>
@@ -3052,9 +2971,6 @@
       <c r="AB32" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH32">
-        <v>200</v>
-      </c>
       <c r="AQ32" t="str">
         <v>https://m.media-amazon.com/images/I/71Bg9MUa6vL._AC_SL1500_.jpg</v>
       </c>
@@ -3144,9 +3060,6 @@
       <c r="AB33" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH33">
-        <v>170</v>
-      </c>
       <c r="AQ33" t="str">
         <v>https://m.media-amazon.com/images/I/710K8Moy-EL._AC_SL1500_.jpg</v>
       </c>
@@ -3236,9 +3149,6 @@
       <c r="AB34" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH34">
-        <v>140</v>
-      </c>
       <c r="AQ34" t="str">
         <v>https://m.media-amazon.com/images/I/81PeVE5VKVL._AC_SL1500_.jpg</v>
       </c>
@@ -3328,9 +3238,6 @@
       <c r="AB35" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH35">
-        <v>310</v>
-      </c>
       <c r="AQ35" t="str">
         <v>https://m.media-amazon.com/images/I/61qb5NSapnL._AC_SL1001_.jpg</v>
       </c>
@@ -3420,9 +3327,6 @@
       <c r="AB36" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH36">
-        <v>200</v>
-      </c>
       <c r="AQ36" t="str">
         <v>https://m.media-amazon.com/images/I/71PGMbAus3L._AC_SL1500_.jpg</v>
       </c>
@@ -3512,9 +3416,6 @@
       <c r="AB37" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH37">
-        <v>250</v>
-      </c>
       <c r="AQ37" t="str">
         <v>https://m.media-amazon.com/images/I/812xTZ6EVbL._AC_SL1500_.jpg</v>
       </c>
@@ -3604,9 +3505,6 @@
       <c r="AB38" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH38">
-        <v>175</v>
-      </c>
       <c r="AQ38" t="str">
         <v>https://m.media-amazon.com/images/I/81+cXBMJNuL._AC_SL1500_.jpg</v>
       </c>
@@ -3696,9 +3594,6 @@
       <c r="AB39" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH39">
-        <v>160</v>
-      </c>
       <c r="AQ39" t="str">
         <v>https://m.media-amazon.com/images/I/81+cXBMJNuL._AC_SL1500_.jpg</v>
       </c>
@@ -3788,9 +3683,6 @@
       <c r="AB40" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH40">
-        <v>180</v>
-      </c>
       <c r="AQ40" t="str">
         <v>https://m.media-amazon.com/images/I/81Bx1kgSMzL._AC_SL1500_.jpg</v>
       </c>
@@ -3880,9 +3772,6 @@
       <c r="AB41" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH41">
-        <v>180</v>
-      </c>
       <c r="AQ41" t="str">
         <v>https://m.media-amazon.com/images/I/71a9nMZv1PL._AC_SL1500_.jpg</v>
       </c>
@@ -3972,9 +3861,6 @@
       <c r="AB42" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH42">
-        <v>300</v>
-      </c>
       <c r="AQ42" t="str">
         <v>https://m.media-amazon.com/images/I/71la5W+vCNL._AC_SL1500_.jpg</v>
       </c>
@@ -4064,9 +3950,6 @@
       <c r="AB43" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH43">
-        <v>75</v>
-      </c>
       <c r="AQ43" t="str">
         <v>https://m.media-amazon.com/images/I/71lksC8OK3L._AC_SL1500_.jpg</v>
       </c>
@@ -4156,9 +4039,6 @@
       <c r="AB44" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH44">
-        <v>120</v>
-      </c>
       <c r="AQ44" t="str">
         <v>https://m.media-amazon.com/images/I/71lksC8OK3L._AC_SL1500_.jpg</v>
       </c>
@@ -4248,9 +4128,6 @@
       <c r="AB45" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH45">
-        <v>135</v>
-      </c>
       <c r="AQ45" t="str">
         <v>https://m.media-amazon.com/images/I/816L-5EYi3L._AC_SL1500_.jpg</v>
       </c>
@@ -4340,9 +4217,6 @@
       <c r="AB46" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH46">
-        <v>85</v>
-      </c>
       <c r="AQ46" t="str">
         <v>https://m.media-amazon.com/images/I/91tXhg6QX8L._AC_SL1500_.jpg</v>
       </c>
@@ -4432,9 +4306,6 @@
       <c r="AB47" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH47">
-        <v>140</v>
-      </c>
       <c r="AQ47" t="str">
         <v>https://m.media-amazon.com/images/I/91tXhg6QX8L._AC_SL1500_.jpg</v>
       </c>
@@ -4524,9 +4395,6 @@
       <c r="AB48" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH48">
-        <v>80</v>
-      </c>
       <c r="AQ48" t="str">
         <v>https://m.media-amazon.com/images/I/81fGvGZ+u3L._AC_SL1500_.jpg</v>
       </c>
@@ -4616,9 +4484,6 @@
       <c r="AB49" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH49">
-        <v>70</v>
-      </c>
       <c r="AQ49" t="str">
         <v>https://m.media-amazon.com/images/I/91eVou9c1kL._AC_SL1500_.jpg</v>
       </c>
@@ -4708,9 +4573,6 @@
       <c r="AB50" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH50">
-        <v>75</v>
-      </c>
       <c r="AQ50" t="str">
         <v>https://m.media-amazon.com/images/I/91cQpcrpcWL._AC_SL1500_.jpg</v>
       </c>
@@ -4800,9 +4662,6 @@
       <c r="AB51" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH51">
-        <v>115</v>
-      </c>
       <c r="AQ51" t="str">
         <v>https://m.media-amazon.com/images/I/91q-Zcejr6L._AC_SL1500_.jpg</v>
       </c>
@@ -4892,9 +4751,6 @@
       <c r="AB52" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH52">
-        <v>90</v>
-      </c>
       <c r="AQ52" t="str">
         <v>https://m.media-amazon.com/images/I/813K6KtVTML._AC_SL1500_.jpg</v>
       </c>
@@ -4984,9 +4840,6 @@
       <c r="AB53" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH53">
-        <v>80</v>
-      </c>
       <c r="AQ53" t="str">
         <v>https://m.media-amazon.com/images/I/81qnYGP0CSL._AC_SL1500_.jpg</v>
       </c>
@@ -5070,9 +4923,6 @@
       <c r="AB54" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH54">
-        <v>130</v>
-      </c>
       <c r="AQ54" t="str">
         <v>https://m.media-amazon.com/images/I/81MT2SNxR4L._AC_SL1500_.jpg</v>
       </c>
@@ -5150,9 +5000,6 @@
       <c r="AB55" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH55">
-        <v>75</v>
-      </c>
       <c r="AQ55" t="str">
         <v>https://m.media-amazon.com/images/I/8121dLMOyOL._AC_SL1500_.jpg</v>
       </c>
@@ -5230,9 +5077,6 @@
       <c r="AB56" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH56">
-        <v>75</v>
-      </c>
       <c r="AQ56" t="str">
         <v>https://m.media-amazon.com/images/I/81dIvrXiqTL._AC_SL1500_.jpg</v>
       </c>
@@ -5304,9 +5148,6 @@
       <c r="AB57" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH57">
-        <v>85</v>
-      </c>
       <c r="AQ57" t="str">
         <v>https://m.media-amazon.com/images/I/81B+DjIVRNL._AC_SL1500_.jpg</v>
       </c>
@@ -5378,9 +5219,6 @@
       <c r="AB58" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH58">
-        <v>85</v>
-      </c>
       <c r="AQ58" t="str">
         <v>https://m.media-amazon.com/images/I/81B+DjIVRNL._AC_SL1500_.jpg</v>
       </c>
@@ -5446,9 +5284,6 @@
       <c r="AB59" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH59">
-        <v>80</v>
-      </c>
       <c r="AQ59" t="str">
         <v>https://m.media-amazon.com/images/I/81hD4FRcrgL._AC_SL1500_.jpg</v>
       </c>
@@ -5508,9 +5343,6 @@
       <c r="AB60" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH60">
-        <v>70</v>
-      </c>
       <c r="AQ60" t="str">
         <v>https://m.media-amazon.com/images/I/81uoDllRQEL._AC_SL1500_.jpg</v>
       </c>
@@ -5564,11 +5396,58 @@
       <c r="AB61" t="str">
         <v>N/A</v>
       </c>
-      <c r="AH61">
-        <v>55</v>
-      </c>
       <c r="AQ61" t="str">
         <v>https://m.media-amazon.com/images/I/81uoDllRQEL._AC_SL1500_.jpg</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>Méga Évolution</v>
+      </c>
+      <c r="B62" t="str">
+        <v>ME04</v>
+      </c>
+      <c r="C62" t="str">
+        <v>Chaos Ascendant (ME04)</v>
+      </c>
+      <c r="D62">
+        <v>46164</v>
+      </c>
+      <c r="E62">
+        <v>60</v>
+      </c>
+      <c r="F62" t="str">
+        <v>🆕 Récent</v>
+      </c>
+      <c r="S62">
+        <v>55</v>
+      </c>
+      <c r="T62">
+        <v>55</v>
+      </c>
+      <c r="U62" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="V62" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="W62" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="X62" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Y62" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="Z62" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AA62" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="AB62" t="str">
+        <v>N/A</v>
       </c>
     </row>
   </sheetData>
